--- a/Daily_Report/Top 7 broker List with its Turnover 2024-06-19.xlsx
+++ b/Daily_Report/Top 7 broker List with its Turnover 2024-06-19.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="283">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="514" uniqueCount="276">
   <si>
     <t>Date: 2024-06-19</t>
   </si>
@@ -62,106 +62,106 @@
     <t>Naasa Securities Co. Ltd.</t>
   </si>
   <si>
-    <t>ABC Securities Pvt. Limited</t>
-  </si>
-  <si>
     <t>Linch Stock Market Limited</t>
   </si>
   <si>
+    <t>Vision Securities Pvt.Limited</t>
+  </si>
+  <si>
+    <t>Imperial Securities Co .Pvt.Limited</t>
+  </si>
+  <si>
     <t>Online Securities Pvt.Ltd</t>
   </si>
   <si>
-    <t>Imperial Securities Co .Pvt.Limited</t>
-  </si>
-  <si>
-    <t>Araya Tara Investment And Securities Pvt. Ltd.</t>
-  </si>
-  <si>
-    <t>Dakshinkali Investment Securities Pvt.Limited</t>
+    <t>Dipshika Dhitopatra Karobar Co. Pvt.Limited</t>
+  </si>
+  <si>
+    <t>Dynamic Money Managers Securities Pvt.Ltd</t>
   </si>
   <si>
     <t>58</t>
   </si>
   <si>
-    <t>17</t>
-  </si>
-  <si>
     <t>41</t>
   </si>
   <si>
+    <t>34</t>
+  </si>
+  <si>
+    <t>45</t>
+  </si>
+  <si>
     <t>49</t>
   </si>
   <si>
-    <t>45</t>
-  </si>
-  <si>
-    <t>57</t>
-  </si>
-  <si>
-    <t>33</t>
-  </si>
-  <si>
-    <t>599,578,064.75</t>
-  </si>
-  <si>
-    <t>522,070,398.4</t>
-  </si>
-  <si>
-    <t>334,584,730.39</t>
-  </si>
-  <si>
-    <t>266,687,048.4</t>
-  </si>
-  <si>
-    <t>247,853,131.89</t>
-  </si>
-  <si>
-    <t>234,915,311.3</t>
-  </si>
-  <si>
-    <t>222,548,959.8</t>
-  </si>
-  <si>
-    <t>266,614,455.85</t>
-  </si>
-  <si>
-    <t>295,289,377.2</t>
-  </si>
-  <si>
-    <t>157,677,050.3</t>
-  </si>
-  <si>
-    <t>71,105,240.5</t>
-  </si>
-  <si>
-    <t>117,640,943.1</t>
-  </si>
-  <si>
-    <t>119,363,534.3</t>
-  </si>
-  <si>
-    <t>78,514,299.4</t>
-  </si>
-  <si>
-    <t>332,963,608.89</t>
-  </si>
-  <si>
-    <t>226,781,021.2</t>
-  </si>
-  <si>
-    <t>176,907,680.1</t>
-  </si>
-  <si>
-    <t>195,581,807.9</t>
-  </si>
-  <si>
-    <t>130,212,188.8</t>
-  </si>
-  <si>
-    <t>115,551,777.0</t>
-  </si>
-  <si>
-    <t>144,034,660.4</t>
+    <t>38</t>
+  </si>
+  <si>
+    <t>44</t>
+  </si>
+  <si>
+    <t>511,097,847.95</t>
+  </si>
+  <si>
+    <t>286,717,452.7</t>
+  </si>
+  <si>
+    <t>261,940,435.5</t>
+  </si>
+  <si>
+    <t>246,510,427.4</t>
+  </si>
+  <si>
+    <t>229,873,873.0</t>
+  </si>
+  <si>
+    <t>214,133,402.05</t>
+  </si>
+  <si>
+    <t>189,887,892.8</t>
+  </si>
+  <si>
+    <t>234,152,676.35</t>
+  </si>
+  <si>
+    <t>163,719,719.5</t>
+  </si>
+  <si>
+    <t>116,730,119.2</t>
+  </si>
+  <si>
+    <t>119,659,130.0</t>
+  </si>
+  <si>
+    <t>110,889,471.5</t>
+  </si>
+  <si>
+    <t>88,333,918.6</t>
+  </si>
+  <si>
+    <t>76,628,510.8</t>
+  </si>
+  <si>
+    <t>276,945,171.6</t>
+  </si>
+  <si>
+    <t>122,997,733.2</t>
+  </si>
+  <si>
+    <t>145,210,316.3</t>
+  </si>
+  <si>
+    <t>126,851,297.4</t>
+  </si>
+  <si>
+    <t>118,984,401.5</t>
+  </si>
+  <si>
+    <t>125,799,483.45</t>
+  </si>
+  <si>
+    <t>113,259,382.0</t>
   </si>
   <si>
     <t>Top 5 Buy</t>
@@ -179,361 +179,331 @@
     <t>% of turnover</t>
   </si>
   <si>
-    <t>PPL</t>
-  </si>
-  <si>
-    <t>110,313,232.0</t>
-  </si>
-  <si>
     <t>GILB</t>
   </si>
   <si>
-    <t>26,342,420.6</t>
+    <t>32,636,824.8</t>
+  </si>
+  <si>
+    <t>NRN</t>
+  </si>
+  <si>
+    <t>23,002,416.5</t>
+  </si>
+  <si>
+    <t>NRIC</t>
+  </si>
+  <si>
+    <t>15,925,026.0</t>
+  </si>
+  <si>
+    <t>SSHL</t>
+  </si>
+  <si>
+    <t>9,766,281.1</t>
+  </si>
+  <si>
+    <t>MKLB</t>
+  </si>
+  <si>
+    <t>9,391,289.5</t>
+  </si>
+  <si>
+    <t>NFS</t>
+  </si>
+  <si>
+    <t>96,777,837.1</t>
+  </si>
+  <si>
+    <t>PFL</t>
+  </si>
+  <si>
+    <t>15,857,186.5</t>
+  </si>
+  <si>
+    <t>GUFL</t>
+  </si>
+  <si>
+    <t>4,104,301.5</t>
+  </si>
+  <si>
+    <t>GFCL</t>
+  </si>
+  <si>
+    <t>2,670,907.4</t>
+  </si>
+  <si>
+    <t>HDL</t>
+  </si>
+  <si>
+    <t>2,205,335.5</t>
+  </si>
+  <si>
+    <t>SICL</t>
+  </si>
+  <si>
+    <t>6,826,030.0</t>
+  </si>
+  <si>
+    <t>SCB</t>
+  </si>
+  <si>
+    <t>5,040,000.0</t>
   </si>
   <si>
     <t>HLBSL</t>
   </si>
   <si>
-    <t>15,648,260.0</t>
-  </si>
-  <si>
-    <t>MKLB</t>
-  </si>
-  <si>
-    <t>9,244,510.5</t>
-  </si>
-  <si>
-    <t>MMKJL</t>
-  </si>
-  <si>
-    <t>8,706,850.6</t>
-  </si>
-  <si>
-    <t>BBC</t>
-  </si>
-  <si>
-    <t>128,442,425.0</t>
+    <t>4,902,913.0</t>
+  </si>
+  <si>
+    <t>FOWAD</t>
+  </si>
+  <si>
+    <t>4,328,985.8</t>
+  </si>
+  <si>
+    <t>MKCL</t>
+  </si>
+  <si>
+    <t>3,100,057.0</t>
+  </si>
+  <si>
+    <t>6,657,698.7</t>
+  </si>
+  <si>
+    <t>CHDC</t>
+  </si>
+  <si>
+    <t>6,106,188.8</t>
+  </si>
+  <si>
+    <t>4,273,024.8</t>
+  </si>
+  <si>
+    <t>MEN</t>
+  </si>
+  <si>
+    <t>3,602,187.1</t>
+  </si>
+  <si>
+    <t>3,555,461.0</t>
   </si>
   <si>
     <t>BFC</t>
   </si>
   <si>
-    <t>96,595,020.0</t>
+    <t>5,012,611.59</t>
+  </si>
+  <si>
+    <t>SGIC</t>
+  </si>
+  <si>
+    <t>3,894,800.0</t>
+  </si>
+  <si>
+    <t>KBSH</t>
+  </si>
+  <si>
+    <t>3,333,563.0</t>
+  </si>
+  <si>
+    <t>3,178,127.5</t>
+  </si>
+  <si>
+    <t>PROFL</t>
+  </si>
+  <si>
+    <t>2,983,076.0</t>
+  </si>
+  <si>
+    <t>15,074,466.0</t>
+  </si>
+  <si>
+    <t>5,130,814.0</t>
+  </si>
+  <si>
+    <t>ANLB</t>
+  </si>
+  <si>
+    <t>3,617,018.1</t>
+  </si>
+  <si>
+    <t>GCIL</t>
+  </si>
+  <si>
+    <t>1,836,550.6</t>
+  </si>
+  <si>
+    <t>JFL</t>
+  </si>
+  <si>
+    <t>1,790,029.0</t>
+  </si>
+  <si>
+    <t>11,529,380.0</t>
+  </si>
+  <si>
+    <t>MLBBL</t>
+  </si>
+  <si>
+    <t>6,681,600.0</t>
+  </si>
+  <si>
+    <t>SWBBL</t>
+  </si>
+  <si>
+    <t>5,195,477.2</t>
+  </si>
+  <si>
+    <t>UNHPL</t>
+  </si>
+  <si>
+    <t>3,512,335.2</t>
+  </si>
+  <si>
+    <t>MKHL</t>
+  </si>
+  <si>
+    <t>2,706,741.2</t>
+  </si>
+  <si>
+    <t>Sell Amount</t>
+  </si>
+  <si>
+    <t>36,066,407.79</t>
+  </si>
+  <si>
+    <t>31,085,629.0</t>
+  </si>
+  <si>
+    <t>17,061,147.89</t>
+  </si>
+  <si>
+    <t>16,243,013.5</t>
+  </si>
+  <si>
+    <t>GLH</t>
+  </si>
+  <si>
+    <t>15,384,178.6</t>
+  </si>
+  <si>
+    <t>23,468,776.8</t>
+  </si>
+  <si>
+    <t>21,680,327.3</t>
+  </si>
+  <si>
+    <t>17,954,392.0</t>
+  </si>
+  <si>
+    <t>SAHAS</t>
+  </si>
+  <si>
+    <t>6,714,083.0</t>
+  </si>
+  <si>
+    <t>SDLBSL</t>
+  </si>
+  <si>
+    <t>2,419,544.0</t>
+  </si>
+  <si>
+    <t>7,797,746.5</t>
+  </si>
+  <si>
+    <t>7,547,840.9</t>
+  </si>
+  <si>
+    <t>7,379,940.6</t>
+  </si>
+  <si>
+    <t>5,663,749.3</t>
+  </si>
+  <si>
+    <t>5,637,378.5</t>
+  </si>
+  <si>
+    <t>SHIVM</t>
+  </si>
+  <si>
+    <t>7,081,249.0</t>
+  </si>
+  <si>
+    <t>6,539,446.4</t>
+  </si>
+  <si>
+    <t>EBL</t>
+  </si>
+  <si>
+    <t>5,436,318.7</t>
+  </si>
+  <si>
+    <t>4,181,857.2</t>
+  </si>
+  <si>
+    <t>HATHY</t>
+  </si>
+  <si>
+    <t>3,622,927.3</t>
+  </si>
+  <si>
+    <t>11,320,762.0</t>
+  </si>
+  <si>
+    <t>8,397,887.5</t>
+  </si>
+  <si>
+    <t>8,381,260.7</t>
   </si>
   <si>
     <t>MHL</t>
   </si>
   <si>
-    <t>22,993,918.9</t>
-  </si>
-  <si>
-    <t>FMDBL</t>
-  </si>
-  <si>
-    <t>18,056,874.0</t>
-  </si>
-  <si>
-    <t>3,998,900.0</t>
-  </si>
-  <si>
-    <t>NFS</t>
-  </si>
-  <si>
-    <t>63,203,943.7</t>
-  </si>
-  <si>
-    <t>PFL</t>
-  </si>
-  <si>
-    <t>43,604,053.0</t>
-  </si>
-  <si>
-    <t>GUFL</t>
-  </si>
-  <si>
-    <t>16,759,612.9</t>
-  </si>
-  <si>
-    <t>NRN</t>
-  </si>
-  <si>
-    <t>11,329,965.0</t>
-  </si>
-  <si>
-    <t>GFCL</t>
-  </si>
-  <si>
-    <t>2,670,907.4</t>
-  </si>
-  <si>
-    <t>SABSL</t>
-  </si>
-  <si>
-    <t>6,507,840.0</t>
-  </si>
-  <si>
-    <t>5,796,960.0</t>
-  </si>
-  <si>
-    <t>IHL</t>
-  </si>
-  <si>
-    <t>4,801,600.0</t>
-  </si>
-  <si>
-    <t>SGIC</t>
-  </si>
-  <si>
-    <t>3,361,250.0</t>
-  </si>
-  <si>
-    <t>KBSH</t>
-  </si>
-  <si>
-    <t>3,333,563.0</t>
-  </si>
-  <si>
-    <t>MKCL</t>
-  </si>
-  <si>
-    <t>21,556,259.0</t>
-  </si>
-  <si>
-    <t>SDLBSL</t>
-  </si>
-  <si>
-    <t>10,673,100.0</t>
-  </si>
-  <si>
-    <t>ULHC</t>
-  </si>
-  <si>
-    <t>9,619,885.0</t>
-  </si>
-  <si>
-    <t>5,874,331.0</t>
-  </si>
-  <si>
-    <t>JOSHI</t>
-  </si>
-  <si>
-    <t>5,637,000.0</t>
-  </si>
-  <si>
-    <t>SAPDBL</t>
-  </si>
-  <si>
-    <t>43,765,271.0</t>
-  </si>
-  <si>
-    <t>20,451,770.0</t>
-  </si>
-  <si>
-    <t>NHDL</t>
-  </si>
-  <si>
-    <t>13,274,792.0</t>
-  </si>
-  <si>
-    <t>TVCL</t>
-  </si>
-  <si>
-    <t>6,177,600.0</t>
-  </si>
-  <si>
-    <t>4,901,280.0</t>
-  </si>
-  <si>
-    <t>LLBS</t>
-  </si>
-  <si>
-    <t>37,089,900.0</t>
-  </si>
-  <si>
-    <t>SMHL</t>
-  </si>
-  <si>
-    <t>19,504,794.0</t>
-  </si>
-  <si>
-    <t>RLFL</t>
-  </si>
-  <si>
-    <t>2,035,340.0</t>
-  </si>
-  <si>
-    <t>ALBSL</t>
-  </si>
-  <si>
-    <t>1,570,500.0</t>
-  </si>
-  <si>
-    <t>LBBL</t>
-  </si>
-  <si>
-    <t>1,235,034.0</t>
-  </si>
-  <si>
-    <t>Sell Amount</t>
-  </si>
-  <si>
-    <t>CHL</t>
-  </si>
-  <si>
-    <t>54,534,644.9</t>
-  </si>
-  <si>
-    <t>38,220,784.0</t>
-  </si>
-  <si>
-    <t>GLH</t>
-  </si>
-  <si>
-    <t>34,603,572.4</t>
-  </si>
-  <si>
-    <t>31,156,941.0</t>
-  </si>
-  <si>
-    <t>27,061,395.0</t>
-  </si>
-  <si>
-    <t>128,304,000.0</t>
-  </si>
-  <si>
-    <t>SONA</t>
-  </si>
-  <si>
-    <t>40,109,335.0</t>
-  </si>
-  <si>
-    <t>15,200,203.3</t>
-  </si>
-  <si>
-    <t>SHLB</t>
-  </si>
-  <si>
-    <t>6,043,131.0</t>
-  </si>
-  <si>
-    <t>ALICL</t>
-  </si>
-  <si>
-    <t>2,435,266.0</t>
-  </si>
-  <si>
-    <t>107,614,656.4</t>
-  </si>
-  <si>
-    <t>JFL</t>
-  </si>
-  <si>
-    <t>21,952,639.8</t>
-  </si>
-  <si>
-    <t>15,246,640.0</t>
-  </si>
-  <si>
-    <t>SAHAS</t>
-  </si>
-  <si>
-    <t>3,853,697.0</t>
-  </si>
-  <si>
-    <t>MSLB</t>
-  </si>
-  <si>
-    <t>3,360,360.0</t>
-  </si>
-  <si>
-    <t>36,988,237.0</t>
-  </si>
-  <si>
-    <t>MPFL</t>
-  </si>
-  <si>
-    <t>31,399,476.8</t>
-  </si>
-  <si>
-    <t>30,589,290.0</t>
-  </si>
-  <si>
-    <t>26,840,680.0</t>
-  </si>
-  <si>
-    <t>SPDL</t>
-  </si>
-  <si>
-    <t>14,300,060.0</t>
-  </si>
-  <si>
-    <t>19,521,000.0</t>
-  </si>
-  <si>
-    <t>BHL</t>
-  </si>
-  <si>
-    <t>10,850,579.0</t>
-  </si>
-  <si>
-    <t>NGPL</t>
-  </si>
-  <si>
-    <t>10,166,571.9</t>
-  </si>
-  <si>
-    <t>MSHL</t>
-  </si>
-  <si>
-    <t>9,159,443.0</t>
-  </si>
-  <si>
-    <t>7,590,000.0</t>
-  </si>
-  <si>
-    <t>JALPA</t>
-  </si>
-  <si>
-    <t>20,775,109.0</t>
-  </si>
-  <si>
-    <t>HIDCL</t>
-  </si>
-  <si>
-    <t>13,732,597.5</t>
-  </si>
-  <si>
-    <t>10,012,926.0</t>
-  </si>
-  <si>
-    <t>8,360,078.8</t>
-  </si>
-  <si>
-    <t>UMRH</t>
-  </si>
-  <si>
-    <t>6,867,420.0</t>
-  </si>
-  <si>
-    <t>87,919,339.0</t>
-  </si>
-  <si>
-    <t>14,787,632.0</t>
-  </si>
-  <si>
-    <t>9,321,900.0</t>
-  </si>
-  <si>
-    <t>CHDC</t>
-  </si>
-  <si>
-    <t>9,193,312.0</t>
-  </si>
-  <si>
-    <t>SWBBL</t>
-  </si>
-  <si>
-    <t>3,217,140.0</t>
+    <t>5,980,276.0</t>
+  </si>
+  <si>
+    <t>4,296,504.0</t>
+  </si>
+  <si>
+    <t>19,109,479.7</t>
+  </si>
+  <si>
+    <t>8,701,157.6</t>
+  </si>
+  <si>
+    <t>3,557,620.0</t>
+  </si>
+  <si>
+    <t>2,851,955.0</t>
+  </si>
+  <si>
+    <t>USHEC</t>
+  </si>
+  <si>
+    <t>2,643,637.0</t>
+  </si>
+  <si>
+    <t>GUFLPO</t>
+  </si>
+  <si>
+    <t>19,525,000.0</t>
+  </si>
+  <si>
+    <t>10,498,990.0</t>
+  </si>
+  <si>
+    <t>HLI</t>
+  </si>
+  <si>
+    <t>10,247,006.9</t>
+  </si>
+  <si>
+    <t>9,492,711.4</t>
+  </si>
+  <si>
+    <t>6,272,213.0</t>
   </si>
   <si>
     <t>Top Traded Stocks</t>
@@ -551,106 +521,109 @@
     <t>Percentage (%)</t>
   </si>
   <si>
-    <t>240,644,906.2</t>
-  </si>
-  <si>
-    <t>225,386,900.4</t>
-  </si>
-  <si>
-    <t>210,945,748.5</t>
-  </si>
-  <si>
-    <t>143,835,605.0</t>
-  </si>
-  <si>
-    <t>128,798,045.0</t>
+    <t>202,338,140.6</t>
+  </si>
+  <si>
+    <t>96,684,518.0</t>
+  </si>
+  <si>
+    <t>89,904,461.1</t>
+  </si>
+  <si>
+    <t>77,453,995.8</t>
+  </si>
+  <si>
+    <t>74,897,934.9</t>
+  </si>
+  <si>
+    <t>Promoter Shares/debenture</t>
+  </si>
+  <si>
+    <t>772,847,704.5</t>
   </si>
   <si>
     <t>Finance</t>
   </si>
   <si>
-    <t>984,924,160.7</t>
+    <t>744,097,021.3</t>
   </si>
   <si>
     <t>Hydro Power</t>
   </si>
   <si>
-    <t>927,657,866.1</t>
+    <t>721,039,108.4</t>
   </si>
   <si>
     <t>Microfinance</t>
   </si>
   <si>
-    <t>662,453,304.79</t>
-  </si>
-  <si>
-    <t>Promoter Shares/debenture</t>
-  </si>
-  <si>
-    <t>581,039,727.79</t>
+    <t>491,144,575.2</t>
   </si>
   <si>
     <t>Investment</t>
   </si>
   <si>
-    <t>185,112,585.9</t>
+    <t>185,544,017.2</t>
   </si>
   <si>
     <t>Development Banks</t>
   </si>
   <si>
-    <t>152,293,912.8</t>
+    <t>124,135,973.4</t>
+  </si>
+  <si>
+    <t>Commercial Banks</t>
+  </si>
+  <si>
+    <t>101,790,918.1</t>
+  </si>
+  <si>
+    <t>Non Life Insurance</t>
+  </si>
+  <si>
+    <t>75,672,907.3</t>
+  </si>
+  <si>
+    <t>Manufacturing And Processing</t>
+  </si>
+  <si>
+    <t>62,751,869.34</t>
+  </si>
+  <si>
+    <t>Hotels And Tourism</t>
+  </si>
+  <si>
+    <t>38,092,777.5</t>
+  </si>
+  <si>
+    <t>Others</t>
+  </si>
+  <si>
+    <t>35,996,546.4</t>
+  </si>
+  <si>
+    <t>Life Insurance</t>
+  </si>
+  <si>
+    <t>32,811,705.3</t>
+  </si>
+  <si>
+    <t>Trading</t>
+  </si>
+  <si>
+    <t>12,557,350.0</t>
   </si>
   <si>
     <t>Tradings</t>
   </si>
   <si>
-    <t>Non Life Insurance</t>
-  </si>
-  <si>
-    <t>55,765,329.6</t>
-  </si>
-  <si>
-    <t>Commercial Banks</t>
-  </si>
-  <si>
-    <t>43,733,067.5</t>
-  </si>
-  <si>
-    <t>Hotels And Tourism</t>
-  </si>
-  <si>
-    <t>39,998,971.79</t>
-  </si>
-  <si>
-    <t>Manufacturing And Processing</t>
-  </si>
-  <si>
-    <t>35,204,595.5</t>
-  </si>
-  <si>
-    <t>Life Insurance</t>
-  </si>
-  <si>
-    <t>15,303,142.4</t>
-  </si>
-  <si>
-    <t>Others</t>
-  </si>
-  <si>
-    <t>9,408,485.4</t>
-  </si>
-  <si>
-    <t>Trading</t>
-  </si>
-  <si>
-    <t>5,242,061.5</t>
+    <t>4,207,227.5</t>
   </si>
   <si>
     <t>Mutual Fund</t>
   </si>
   <si>
-    <t>698,390.0</t>
+    <t>1,682,931.2</t>
   </si>
   <si>
     <t>Total</t>
@@ -662,208 +635,214 @@
     <t>100%</t>
   </si>
   <si>
-    <t>124,446,063.6</t>
-  </si>
-  <si>
-    <t>54,988,522.0</t>
-  </si>
-  <si>
-    <t>47,339,113.8</t>
-  </si>
-  <si>
-    <t>17,111,959.3</t>
-  </si>
-  <si>
-    <t>9,476,024.8</t>
-  </si>
-  <si>
-    <t>104,749,220.1</t>
-  </si>
-  <si>
-    <t>27,603,305.3</t>
-  </si>
-  <si>
-    <t>23,524,705.3</t>
-  </si>
-  <si>
-    <t>6,312,104.0</t>
-  </si>
-  <si>
-    <t>129,126,589.8</t>
-  </si>
-  <si>
-    <t>11,458,290.0</t>
-  </si>
-  <si>
-    <t>4,538,932.5</t>
-  </si>
-  <si>
-    <t>4,380,054.3</t>
-  </si>
-  <si>
-    <t>3,919,317.4</t>
-  </si>
-  <si>
-    <t>24,444,735.6</t>
-  </si>
-  <si>
-    <t>17,854,002.39</t>
-  </si>
-  <si>
-    <t>12,418,364.6</t>
-  </si>
-  <si>
-    <t>7,257,935.3</t>
-  </si>
-  <si>
-    <t>4,080,957.7</t>
-  </si>
-  <si>
-    <t>42,940,027.5</t>
-  </si>
-  <si>
-    <t>24,441,070.7</t>
-  </si>
-  <si>
-    <t>20,013,482.0</t>
-  </si>
-  <si>
-    <t>18,968,785.6</t>
-  </si>
-  <si>
-    <t>5,493,475.4</t>
-  </si>
-  <si>
-    <t>45,711,839.0</t>
-  </si>
-  <si>
-    <t>21,388,549.89</t>
-  </si>
-  <si>
-    <t>20,978,861.6</t>
-  </si>
-  <si>
-    <t>17,691,393.89</t>
-  </si>
-  <si>
-    <t>6,018,334.1</t>
-  </si>
-  <si>
-    <t>43,224,989.2</t>
-  </si>
-  <si>
-    <t>25,325,454.1</t>
-  </si>
-  <si>
-    <t>3,121,128.3</t>
-  </si>
-  <si>
-    <t>2,222,429.7</t>
-  </si>
-  <si>
-    <t>2,146,042.5</t>
-  </si>
-  <si>
-    <t>145,970,006.4</t>
-  </si>
-  <si>
-    <t>51,343,102.7</t>
-  </si>
-  <si>
-    <t>46,074,325.2</t>
-  </si>
-  <si>
-    <t>33,525,958.4</t>
-  </si>
-  <si>
-    <t>25,765,077.1</t>
-  </si>
-  <si>
-    <t>48,585,163.4</t>
-  </si>
-  <si>
-    <t>24,428,615.6</t>
-  </si>
-  <si>
-    <t>10,629,791.3</t>
-  </si>
-  <si>
-    <t>4,629,168.09</t>
-  </si>
-  <si>
-    <t>149,325,391.1</t>
-  </si>
-  <si>
-    <t>9,857,690.6</t>
-  </si>
-  <si>
-    <t>7,785,628.0</t>
-  </si>
-  <si>
-    <t>6,617,008.1</t>
-  </si>
-  <si>
-    <t>1,002,624.7</t>
-  </si>
-  <si>
-    <t>56,917,037.1</t>
-  </si>
-  <si>
-    <t>51,933,921.6</t>
-  </si>
-  <si>
-    <t>38,760,042.2</t>
-  </si>
-  <si>
-    <t>37,363,689.2</t>
-  </si>
-  <si>
-    <t>3,945,401.3</t>
-  </si>
-  <si>
-    <t>53,298,889.7</t>
-  </si>
-  <si>
-    <t>28,259,041.2</t>
-  </si>
-  <si>
-    <t>19,525,726.6</t>
-  </si>
-  <si>
-    <t>17,164,309.7</t>
-  </si>
-  <si>
-    <t>5,288,336.8</t>
-  </si>
-  <si>
-    <t>25,531,050.8</t>
-  </si>
-  <si>
-    <t>25,259,831.5</t>
-  </si>
-  <si>
-    <t>25,259,032.8</t>
-  </si>
-  <si>
-    <t>18,100,394.3</t>
-  </si>
-  <si>
-    <t>8,863,374.1</t>
-  </si>
-  <si>
-    <t>106,464,826.1</t>
-  </si>
-  <si>
-    <t>17,453,434.0</t>
-  </si>
-  <si>
-    <t>9,496,115.0</t>
-  </si>
-  <si>
-    <t>5,913,634.4</t>
-  </si>
-  <si>
-    <t>2,682,689.0</t>
+    <t>55,135,172.4</t>
+  </si>
+  <si>
+    <t>46,759,127.9</t>
+  </si>
+  <si>
+    <t>45,347,721.0</t>
+  </si>
+  <si>
+    <t>25,943,663.2</t>
+  </si>
+  <si>
+    <t>25,172,999.8</t>
+  </si>
+  <si>
+    <t>123,391,782.2</t>
+  </si>
+  <si>
+    <t>11,541,893.9</t>
+  </si>
+  <si>
+    <t>10,001,346.3</t>
+  </si>
+  <si>
+    <t>6,317,807.2</t>
+  </si>
+  <si>
+    <t>3,390,719.5</t>
+  </si>
+  <si>
+    <t>30,101,974.6</t>
+  </si>
+  <si>
+    <t>23,004,716.5</t>
+  </si>
+  <si>
+    <t>18,851,491.6</t>
+  </si>
+  <si>
+    <t>14,921,062.9</t>
+  </si>
+  <si>
+    <t>8,928,160.4</t>
+  </si>
+  <si>
+    <t>29,281,163.8</t>
+  </si>
+  <si>
+    <t>27,558,545.0</t>
+  </si>
+  <si>
+    <t>24,648,014.9</t>
+  </si>
+  <si>
+    <t>16,127,799.0</t>
+  </si>
+  <si>
+    <t>8,663,940.3</t>
+  </si>
+  <si>
+    <t>32,186,770.1</t>
+  </si>
+  <si>
+    <t>23,528,255.4</t>
+  </si>
+  <si>
+    <t>18,263,881.7</t>
+  </si>
+  <si>
+    <t>17,372,473.3</t>
+  </si>
+  <si>
+    <t>6,479,616.3</t>
+  </si>
+  <si>
+    <t>37,067,805.9</t>
+  </si>
+  <si>
+    <t>16,450,501.0</t>
+  </si>
+  <si>
+    <t>13,513,309.1</t>
+  </si>
+  <si>
+    <t>11,300,109.6</t>
+  </si>
+  <si>
+    <t>2,349,743.6</t>
+  </si>
+  <si>
+    <t>17,899,741.0</t>
+  </si>
+  <si>
+    <t>16,525,221.4</t>
+  </si>
+  <si>
+    <t>15,001,653.9</t>
+  </si>
+  <si>
+    <t>12,303,219.0</t>
+  </si>
+  <si>
+    <t>5,233,166.4</t>
+  </si>
+  <si>
+    <t>79,572,411.9</t>
+  </si>
+  <si>
+    <t>65,006,590.3</t>
+  </si>
+  <si>
+    <t>41,079,662.79</t>
+  </si>
+  <si>
+    <t>32,138,710.1</t>
+  </si>
+  <si>
+    <t>21,282,509.8</t>
+  </si>
+  <si>
+    <t>71,998,410.5</t>
+  </si>
+  <si>
+    <t>17,708,527.89</t>
+  </si>
+  <si>
+    <t>17,232,478.2</t>
+  </si>
+  <si>
+    <t>7,962,463.0</t>
+  </si>
+  <si>
+    <t>2,647,195.79</t>
+  </si>
+  <si>
+    <t>40,341,814.7</t>
+  </si>
+  <si>
+    <t>38,097,820.4</t>
+  </si>
+  <si>
+    <t>22,135,851.6</t>
+  </si>
+  <si>
+    <t>19,763,895.7</t>
+  </si>
+  <si>
+    <t>6,218,340.1</t>
+  </si>
+  <si>
+    <t>30,003,150.9</t>
+  </si>
+  <si>
+    <t>25,739,771.0</t>
+  </si>
+  <si>
+    <t>22,636,329.3</t>
+  </si>
+  <si>
+    <t>16,450,460.5</t>
+  </si>
+  <si>
+    <t>9,272,050.6</t>
+  </si>
+  <si>
+    <t>33,518,685.0</t>
+  </si>
+  <si>
+    <t>31,520,918.0</t>
+  </si>
+  <si>
+    <t>16,933,941.7</t>
+  </si>
+  <si>
+    <t>12,130,809.5</t>
+  </si>
+  <si>
+    <t>10,979,883.4</t>
+  </si>
+  <si>
+    <t>41,627,788.1</t>
+  </si>
+  <si>
+    <t>21,117,326.1</t>
+  </si>
+  <si>
+    <t>17,899,408.8</t>
+  </si>
+  <si>
+    <t>13,993,263.7</t>
+  </si>
+  <si>
+    <t>12,478,786.3</t>
+  </si>
+  <si>
+    <t>45,032,815.1</t>
+  </si>
+  <si>
+    <t>20,161,020.5</t>
+  </si>
+  <si>
+    <t>18,588,670.1</t>
+  </si>
+  <si>
+    <t>10,403,103.1</t>
+  </si>
+  <si>
+    <t>6,186,372.3</t>
   </si>
 </sst>
 </file>
@@ -1672,7 +1651,7 @@
         <v>55</v>
       </c>
       <c r="D9" s="10">
-        <v>0.1839847694328114</v>
+        <v>0.06385631426722974</v>
       </c>
       <c r="E9" s="11" t="s">
         <v>64</v>
@@ -1681,52 +1660,52 @@
         <v>65</v>
       </c>
       <c r="G9" s="12">
-        <v>0.2460251057973028</v>
+        <v>0.3375373078570881</v>
       </c>
       <c r="H9" s="13" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="I9" s="13" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="J9" s="14">
-        <v>0.1889026544171306</v>
+        <v>0.02605947412040551</v>
       </c>
       <c r="K9" s="15" t="s">
-        <v>83</v>
+        <v>68</v>
       </c>
       <c r="L9" s="15" t="s">
         <v>84</v>
       </c>
       <c r="M9" s="16">
-        <v>0.0244025348776555</v>
+        <v>0.02700777719717669</v>
       </c>
       <c r="N9" s="17" t="s">
+        <v>91</v>
+      </c>
+      <c r="O9" s="17" t="s">
         <v>92</v>
       </c>
-      <c r="O9" s="17" t="s">
-        <v>93</v>
-      </c>
       <c r="P9" s="18">
-        <v>0.086971904832323</v>
+        <v>0.02180592137149923</v>
       </c>
       <c r="Q9" s="15" t="s">
-        <v>101</v>
+        <v>78</v>
       </c>
       <c r="R9" s="15" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="S9" s="16">
-        <v>0.1863023349044682</v>
+        <v>0.0703975459021574</v>
       </c>
       <c r="T9" s="17" t="s">
-        <v>109</v>
+        <v>85</v>
       </c>
       <c r="U9" s="17" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="V9" s="18">
-        <v>0.1666595073431568</v>
+        <v>0.06071677256508057</v>
       </c>
     </row>
     <row r="10" spans="1:22">
@@ -1738,7 +1717,7 @@
         <v>57</v>
       </c>
       <c r="D10" s="10">
-        <v>0.04393493049313559</v>
+        <v>0.04500589582261417</v>
       </c>
       <c r="E10" s="11" t="s">
         <v>66</v>
@@ -1747,52 +1726,52 @@
         <v>67</v>
       </c>
       <c r="G10" s="12">
-        <v>0.1850229783110415</v>
+        <v>0.05530596882287383</v>
       </c>
       <c r="H10" s="13" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="I10" s="13" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="J10" s="14">
-        <v>0.1303229019084967</v>
+        <v>0.01924101557813895</v>
       </c>
       <c r="K10" s="15" t="s">
-        <v>66</v>
+        <v>85</v>
       </c>
       <c r="L10" s="15" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="M10" s="16">
-        <v>0.02173693861317639</v>
+        <v>0.02477050916021413</v>
       </c>
       <c r="N10" s="17" t="s">
+        <v>93</v>
+      </c>
+      <c r="O10" s="17" t="s">
         <v>94</v>
       </c>
-      <c r="O10" s="17" t="s">
-        <v>95</v>
-      </c>
       <c r="P10" s="18">
-        <v>0.04306219541460634</v>
+        <v>0.01694320432840143</v>
       </c>
       <c r="Q10" s="15" t="s">
-        <v>79</v>
+        <v>68</v>
       </c>
       <c r="R10" s="15" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="S10" s="16">
-        <v>0.08706018303711989</v>
+        <v>0.02396082979525986</v>
       </c>
       <c r="T10" s="17" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="U10" s="17" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="V10" s="18">
-        <v>0.08764271024914491</v>
+        <v>0.0351870774986029</v>
       </c>
     </row>
     <row r="11" spans="1:22">
@@ -1804,7 +1783,7 @@
         <v>59</v>
       </c>
       <c r="D11" s="10">
-        <v>0.02609878666345924</v>
+        <v>0.03115846811696597</v>
       </c>
       <c r="E11" s="11" t="s">
         <v>68</v>
@@ -1813,52 +1792,52 @@
         <v>69</v>
       </c>
       <c r="G11" s="12">
-        <v>0.04404371320509636</v>
+        <v>0.01431479479658477</v>
       </c>
       <c r="H11" s="13" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I11" s="13" t="s">
+        <v>79</v>
+      </c>
+      <c r="J11" s="14">
+        <v>0.01871766377207539</v>
+      </c>
+      <c r="K11" s="15" t="s">
         <v>78</v>
-      </c>
-      <c r="J11" s="14">
-        <v>0.0500907883033505</v>
-      </c>
-      <c r="K11" s="15" t="s">
-        <v>86</v>
       </c>
       <c r="L11" s="15" t="s">
         <v>87</v>
       </c>
       <c r="M11" s="16">
-        <v>0.01800462387958995</v>
+        <v>0.01733405294481267</v>
       </c>
       <c r="N11" s="17" t="s">
+        <v>95</v>
+      </c>
+      <c r="O11" s="17" t="s">
         <v>96</v>
       </c>
-      <c r="O11" s="17" t="s">
-        <v>97</v>
-      </c>
       <c r="P11" s="18">
-        <v>0.03881284422857842</v>
+        <v>0.01450170459345765</v>
       </c>
       <c r="Q11" s="15" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="R11" s="15" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="S11" s="16">
-        <v>0.05650884110762515</v>
+        <v>0.01689142406262909</v>
       </c>
       <c r="T11" s="17" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="U11" s="17" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="V11" s="18">
-        <v>0.009145583074524889</v>
+        <v>0.02736076072776347</v>
       </c>
     </row>
     <row r="12" spans="1:22">
@@ -1870,7 +1849,7 @@
         <v>61</v>
       </c>
       <c r="D12" s="10">
-        <v>0.01541836008269347</v>
+        <v>0.01910843714011377</v>
       </c>
       <c r="E12" s="11" t="s">
         <v>70</v>
@@ -1879,16 +1858,16 @@
         <v>71</v>
       </c>
       <c r="G12" s="12">
-        <v>0.0345870481363036</v>
+        <v>0.009315468503393272</v>
       </c>
       <c r="H12" s="13" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="I12" s="13" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="J12" s="14">
-        <v>0.03386276769550987</v>
+        <v>0.01652660381256791</v>
       </c>
       <c r="K12" s="15" t="s">
         <v>88</v>
@@ -1897,34 +1876,34 @@
         <v>89</v>
       </c>
       <c r="M12" s="16">
-        <v>0.01260372417845545</v>
+        <v>0.01461271694667469</v>
       </c>
       <c r="N12" s="17" t="s">
-        <v>75</v>
+        <v>56</v>
       </c>
       <c r="O12" s="17" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="P12" s="18">
-        <v>0.0237008544333024</v>
+        <v>0.01382552727077426</v>
       </c>
       <c r="Q12" s="15" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="R12" s="15" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="S12" s="16">
-        <v>0.02629713646936729</v>
+        <v>0.0085766656785809</v>
       </c>
       <c r="T12" s="17" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="U12" s="17" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="V12" s="18">
-        <v>0.007056874143161014</v>
+        <v>0.01849688860205204</v>
       </c>
     </row>
     <row r="13" spans="1:22">
@@ -1936,61 +1915,61 @@
         <v>63</v>
       </c>
       <c r="D13" s="10">
-        <v>0.01452162964572496</v>
+        <v>0.01837473888349993</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>58</v>
+        <v>72</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="G13" s="12">
-        <v>0.007659694961169053</v>
+        <v>0.007691668153551505</v>
       </c>
       <c r="H13" s="13" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="I13" s="13" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="J13" s="14">
-        <v>0.007982753417368744</v>
+        <v>0.01183496925200768</v>
       </c>
       <c r="K13" s="15" t="s">
+        <v>66</v>
+      </c>
+      <c r="L13" s="15" t="s">
         <v>90</v>
       </c>
-      <c r="L13" s="15" t="s">
-        <v>91</v>
-      </c>
       <c r="M13" s="16">
-        <v>0.012499905863445</v>
+        <v>0.0144231667499839</v>
       </c>
       <c r="N13" s="17" t="s">
+        <v>98</v>
+      </c>
+      <c r="O13" s="17" t="s">
         <v>99</v>
       </c>
-      <c r="O13" s="17" t="s">
-        <v>100</v>
-      </c>
       <c r="P13" s="18">
-        <v>0.02274330752566133</v>
+        <v>0.0129770119634257</v>
       </c>
       <c r="Q13" s="15" t="s">
-        <v>58</v>
+        <v>106</v>
       </c>
       <c r="R13" s="15" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="S13" s="16">
-        <v>0.02086402956400229</v>
+        <v>0.008359410455646846</v>
       </c>
       <c r="T13" s="17" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="U13" s="17" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="V13" s="18">
-        <v>0.00554949347375022</v>
+        <v>0.01425441696196441</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -2001,7 +1980,7 @@
         <v>51</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>53</v>
@@ -2010,7 +1989,7 @@
         <v>51</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>53</v>
@@ -2019,7 +1998,7 @@
         <v>51</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="J15" s="4" t="s">
         <v>53</v>
@@ -2028,7 +2007,7 @@
         <v>51</v>
       </c>
       <c r="L15" s="5" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="M15" s="5" t="s">
         <v>53</v>
@@ -2037,7 +2016,7 @@
         <v>51</v>
       </c>
       <c r="O15" s="6" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="P15" s="6" t="s">
         <v>53</v>
@@ -2046,7 +2025,7 @@
         <v>51</v>
       </c>
       <c r="R15" s="5" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="S15" s="5" t="s">
         <v>53</v>
@@ -2055,7 +2034,7 @@
         <v>51</v>
       </c>
       <c r="U15" s="6" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="V15" s="6" t="s">
         <v>53</v>
@@ -2064,566 +2043,566 @@
     <row r="16" spans="1:22">
       <c r="A16" s="1"/>
       <c r="B16" s="9" t="s">
-        <v>120</v>
+        <v>54</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>121</v>
+        <v>118</v>
       </c>
       <c r="D16" s="10">
-        <v>0.09095503672693356</v>
+        <v>0.07056654209103287</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>64</v>
+        <v>106</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>127</v>
+        <v>124</v>
       </c>
       <c r="G16" s="12">
-        <v>0.2457599595633385</v>
+        <v>0.0818533248638896</v>
       </c>
       <c r="H16" s="13" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I16" s="13" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="J16" s="14">
-        <v>0.3216364843408885</v>
+        <v>0.0297691591033489</v>
       </c>
       <c r="K16" s="15" t="s">
-        <v>79</v>
+        <v>136</v>
       </c>
       <c r="L16" s="15" t="s">
-        <v>143</v>
+        <v>137</v>
       </c>
       <c r="M16" s="16">
-        <v>0.1386952880610905</v>
+        <v>0.02872596130998392</v>
       </c>
       <c r="N16" s="17" t="s">
-        <v>109</v>
+        <v>56</v>
       </c>
       <c r="O16" s="17" t="s">
+        <v>144</v>
+      </c>
+      <c r="P16" s="18">
+        <v>0.04924771072178351</v>
+      </c>
+      <c r="Q16" s="15" t="s">
+        <v>78</v>
+      </c>
+      <c r="R16" s="15" t="s">
         <v>150</v>
       </c>
-      <c r="P16" s="18">
-        <v>0.0787603523520374</v>
-      </c>
-      <c r="Q16" s="15" t="s">
-        <v>158</v>
-      </c>
-      <c r="R16" s="15" t="s">
-        <v>159</v>
-      </c>
       <c r="S16" s="16">
-        <v>0.08843658970133718</v>
+        <v>0.08924100358494257</v>
       </c>
       <c r="T16" s="17" t="s">
-        <v>131</v>
+        <v>156</v>
       </c>
       <c r="U16" s="17" t="s">
-        <v>166</v>
+        <v>157</v>
       </c>
       <c r="V16" s="18">
-        <v>0.3950561668722749</v>
+        <v>0.10282382784965</v>
       </c>
     </row>
     <row r="17" spans="1:22">
       <c r="A17" s="1"/>
       <c r="B17" s="9" t="s">
-        <v>56</v>
+        <v>74</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="D17" s="10">
-        <v>0.06374613456870963</v>
+        <v>0.06082128720495231</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>128</v>
+        <v>68</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="G17" s="12">
-        <v>0.07682744534630562</v>
+        <v>0.07561565260795163</v>
       </c>
       <c r="H17" s="13" t="s">
-        <v>136</v>
+        <v>68</v>
       </c>
       <c r="I17" s="13" t="s">
-        <v>137</v>
+        <v>132</v>
       </c>
       <c r="J17" s="14">
-        <v>0.06561160090526355</v>
+        <v>0.02881510403535998</v>
       </c>
       <c r="K17" s="15" t="s">
-        <v>144</v>
+        <v>64</v>
       </c>
       <c r="L17" s="15" t="s">
+        <v>138</v>
+      </c>
+      <c r="M17" s="16">
+        <v>0.02652807213460699</v>
+      </c>
+      <c r="N17" s="17" t="s">
+        <v>98</v>
+      </c>
+      <c r="O17" s="17" t="s">
         <v>145</v>
       </c>
-      <c r="M17" s="16">
-        <v>0.1177390390286385</v>
-      </c>
-      <c r="N17" s="17" t="s">
+      <c r="P17" s="18">
+        <v>0.03653258802491225</v>
+      </c>
+      <c r="Q17" s="15" t="s">
+        <v>76</v>
+      </c>
+      <c r="R17" s="15" t="s">
         <v>151</v>
       </c>
-      <c r="O17" s="17" t="s">
-        <v>152</v>
-      </c>
-      <c r="P17" s="18">
-        <v>0.04377826060466255</v>
-      </c>
-      <c r="Q17" s="15" t="s">
-        <v>160</v>
-      </c>
-      <c r="R17" s="15" t="s">
-        <v>161</v>
-      </c>
       <c r="S17" s="16">
-        <v>0.05845765192573039</v>
+        <v>0.04063428459408815</v>
       </c>
       <c r="T17" s="17" t="s">
-        <v>77</v>
+        <v>109</v>
       </c>
       <c r="U17" s="17" t="s">
-        <v>167</v>
+        <v>158</v>
       </c>
       <c r="V17" s="18">
-        <v>0.0664466462269216</v>
+        <v>0.05529046557517014</v>
       </c>
     </row>
     <row r="18" spans="1:22">
       <c r="A18" s="1"/>
       <c r="B18" s="9" t="s">
-        <v>123</v>
+        <v>58</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="D18" s="10">
-        <v>0.05771320606004541</v>
+        <v>0.03338137299625074</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>68</v>
+        <v>64</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="G18" s="12">
-        <v>0.02911523684657161</v>
+        <v>0.06262050611472944</v>
       </c>
       <c r="H18" s="13" t="s">
-        <v>73</v>
+        <v>64</v>
       </c>
       <c r="I18" s="13" t="s">
-        <v>138</v>
+        <v>133</v>
       </c>
       <c r="J18" s="14">
-        <v>0.04556884583995349</v>
+        <v>0.02817411747030557</v>
       </c>
       <c r="K18" s="15" t="s">
-        <v>68</v>
+        <v>139</v>
       </c>
       <c r="L18" s="15" t="s">
+        <v>140</v>
+      </c>
+      <c r="M18" s="16">
+        <v>0.02205309835100306</v>
+      </c>
+      <c r="N18" s="17" t="s">
+        <v>64</v>
+      </c>
+      <c r="O18" s="17" t="s">
         <v>146</v>
       </c>
-      <c r="M18" s="16">
-        <v>0.1147010707251129</v>
-      </c>
-      <c r="N18" s="17" t="s">
-        <v>153</v>
-      </c>
-      <c r="O18" s="17" t="s">
-        <v>154</v>
-      </c>
       <c r="P18" s="18">
-        <v>0.04101853312106564</v>
+        <v>0.03646025792587573</v>
       </c>
       <c r="Q18" s="15" t="s">
-        <v>153</v>
+        <v>66</v>
       </c>
       <c r="R18" s="15" t="s">
-        <v>162</v>
+        <v>152</v>
       </c>
       <c r="S18" s="16">
-        <v>0.04262355631307885</v>
+        <v>0.01661403576434702</v>
       </c>
       <c r="T18" s="17" t="s">
-        <v>56</v>
+        <v>159</v>
       </c>
       <c r="U18" s="17" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="V18" s="18">
-        <v>0.04188696279855629</v>
+        <v>0.05396345574697957</v>
       </c>
     </row>
     <row r="19" spans="1:22">
       <c r="A19" s="1"/>
       <c r="B19" s="9" t="s">
-        <v>79</v>
+        <v>88</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="D19" s="10">
-        <v>0.05196477795262773</v>
+        <v>0.03178063371847543</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="G19" s="12">
-        <v>0.0115753182301094</v>
+        <v>0.02341707118549606</v>
       </c>
       <c r="H19" s="13" t="s">
-        <v>139</v>
+        <v>66</v>
       </c>
       <c r="I19" s="13" t="s">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="J19" s="14">
-        <v>0.01151785078593653</v>
+        <v>0.02162227946666142</v>
       </c>
       <c r="K19" s="15" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="L19" s="15" t="s">
+        <v>141</v>
+      </c>
+      <c r="M19" s="16">
+        <v>0.01696422031354606</v>
+      </c>
+      <c r="N19" s="17" t="s">
         <v>147</v>
       </c>
-      <c r="M19" s="16">
-        <v>0.1006448575625692</v>
-      </c>
-      <c r="N19" s="17" t="s">
-        <v>155</v>
-      </c>
       <c r="O19" s="17" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="P19" s="18">
-        <v>0.03695512309965691</v>
+        <v>0.02601546631617417</v>
       </c>
       <c r="Q19" s="15" t="s">
-        <v>136</v>
+        <v>82</v>
       </c>
       <c r="R19" s="15" t="s">
-        <v>163</v>
+        <v>153</v>
       </c>
       <c r="S19" s="16">
-        <v>0.03558762838290992</v>
+        <v>0.01331859005973328</v>
       </c>
       <c r="T19" s="17" t="s">
-        <v>169</v>
+        <v>64</v>
       </c>
       <c r="U19" s="17" t="s">
-        <v>170</v>
+        <v>161</v>
       </c>
       <c r="V19" s="18">
-        <v>0.04130916634371975</v>
+        <v>0.0499911356117803</v>
       </c>
     </row>
     <row r="20" spans="1:22">
       <c r="A20" s="1"/>
       <c r="B20" s="9" t="s">
-        <v>54</v>
+        <v>122</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>126</v>
+        <v>123</v>
       </c>
       <c r="D20" s="10">
-        <v>0.0451340644212585</v>
+        <v>0.03010026096119468</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="G20" s="12">
-        <v>0.004664631450975597</v>
+        <v>0.008438774749201027</v>
       </c>
       <c r="H20" s="13" t="s">
-        <v>141</v>
+        <v>129</v>
       </c>
       <c r="I20" s="13" t="s">
+        <v>135</v>
+      </c>
+      <c r="J20" s="14">
+        <v>0.02152160467031063</v>
+      </c>
+      <c r="K20" s="15" t="s">
         <v>142</v>
       </c>
-      <c r="J20" s="14">
-        <v>0.01004337524902183</v>
-      </c>
-      <c r="K20" s="15" t="s">
-        <v>148</v>
-      </c>
       <c r="L20" s="15" t="s">
+        <v>143</v>
+      </c>
+      <c r="M20" s="16">
+        <v>0.01469685212999635</v>
+      </c>
+      <c r="N20" s="17" t="s">
+        <v>106</v>
+      </c>
+      <c r="O20" s="17" t="s">
         <v>149</v>
       </c>
-      <c r="M20" s="16">
-        <v>0.05362112665685793</v>
-      </c>
-      <c r="N20" s="17" t="s">
-        <v>148</v>
-      </c>
-      <c r="O20" s="17" t="s">
-        <v>157</v>
-      </c>
       <c r="P20" s="18">
-        <v>0.03062297394354612</v>
+        <v>0.01869070174843228</v>
       </c>
       <c r="Q20" s="15" t="s">
-        <v>164</v>
+        <v>154</v>
       </c>
       <c r="R20" s="15" t="s">
-        <v>165</v>
+        <v>155</v>
       </c>
       <c r="S20" s="16">
-        <v>0.0292335989595413</v>
+        <v>0.01234574790617072</v>
       </c>
       <c r="T20" s="17" t="s">
-        <v>171</v>
+        <v>78</v>
       </c>
       <c r="U20" s="17" t="s">
-        <v>172</v>
+        <v>162</v>
       </c>
       <c r="V20" s="18">
-        <v>0.01445587525051195</v>
+        <v>0.03303113699095196</v>
       </c>
     </row>
     <row r="23" spans="1:22">
       <c r="B23" s="19" t="s">
-        <v>173</v>
+        <v>163</v>
       </c>
       <c r="C23" s="19" t="s">
-        <v>174</v>
+        <v>164</v>
       </c>
     </row>
     <row r="24" spans="1:22">
       <c r="B24" s="20" t="s">
-        <v>77</v>
+        <v>64</v>
       </c>
       <c r="C24" s="21" t="s">
-        <v>178</v>
+        <v>168</v>
       </c>
     </row>
     <row r="25" spans="1:22">
       <c r="B25" s="20" t="s">
-        <v>75</v>
+        <v>68</v>
       </c>
       <c r="C25" s="21" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
     </row>
     <row r="26" spans="1:22">
       <c r="B26" s="20" t="s">
-        <v>131</v>
+        <v>54</v>
       </c>
       <c r="C26" s="21" t="s">
-        <v>180</v>
+        <v>170</v>
       </c>
     </row>
     <row r="27" spans="1:22">
       <c r="B27" s="20" t="s">
-        <v>68</v>
+        <v>85</v>
       </c>
       <c r="C27" s="21" t="s">
-        <v>181</v>
+        <v>171</v>
       </c>
     </row>
     <row r="28" spans="1:22">
       <c r="B28" s="20" t="s">
-        <v>64</v>
+        <v>78</v>
       </c>
       <c r="C28" s="21" t="s">
-        <v>182</v>
+        <v>172</v>
       </c>
     </row>
     <row r="30" spans="1:22">
       <c r="B30" s="19" t="s">
-        <v>175</v>
+        <v>165</v>
       </c>
       <c r="C30" s="19" t="s">
-        <v>176</v>
+        <v>166</v>
       </c>
       <c r="D30" s="19" t="s">
-        <v>177</v>
+        <v>167</v>
       </c>
     </row>
     <row r="31" spans="1:22">
       <c r="B31" s="20" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="C31" s="21" t="s">
-        <v>184</v>
+        <v>174</v>
       </c>
       <c r="D31" s="22">
-        <v>0.2893115022888131</v>
+        <v>0.2270161900287271</v>
       </c>
     </row>
     <row r="32" spans="1:22">
       <c r="B32" s="20" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="C32" s="21" t="s">
-        <v>186</v>
+        <v>176</v>
       </c>
       <c r="D32" s="22">
-        <v>0.2724901079294091</v>
+        <v>0.2185709678681598</v>
       </c>
     </row>
     <row r="33" spans="2:4">
       <c r="B33" s="20" t="s">
-        <v>187</v>
+        <v>177</v>
       </c>
       <c r="C33" s="21" t="s">
-        <v>188</v>
+        <v>178</v>
       </c>
       <c r="D33" s="22">
-        <v>0.1945889525866283</v>
+        <v>0.211797939358023</v>
       </c>
     </row>
     <row r="34" spans="2:4">
       <c r="B34" s="20" t="s">
-        <v>189</v>
+        <v>179</v>
       </c>
       <c r="C34" s="21" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="D34" s="22">
-        <v>0.1706745384536296</v>
+        <v>0.1442687473430694</v>
       </c>
     </row>
     <row r="35" spans="2:4">
       <c r="B35" s="20" t="s">
-        <v>191</v>
+        <v>181</v>
       </c>
       <c r="C35" s="21" t="s">
-        <v>192</v>
+        <v>182</v>
       </c>
       <c r="D35" s="22">
-        <v>0.05437494830184032</v>
+        <v>0.05450167687904234</v>
       </c>
     </row>
     <row r="36" spans="2:4">
       <c r="B36" s="20" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="C36" s="21" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="D36" s="22">
-        <v>0.04473479528646668</v>
+        <v>0.03646368561708707</v>
       </c>
     </row>
     <row r="37" spans="2:4">
       <c r="B37" s="20" t="s">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="C37" s="21" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="D37" s="22">
-        <v>0.03783312195766318</v>
+        <v>0.02990005181103335</v>
       </c>
     </row>
     <row r="38" spans="2:4">
       <c r="B38" s="20" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="C38" s="21" t="s">
-        <v>197</v>
+        <v>188</v>
       </c>
       <c r="D38" s="22">
-        <v>0.01638050108420578</v>
+        <v>0.02222815051868094</v>
       </c>
     </row>
     <row r="39" spans="2:4">
       <c r="B39" s="20" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="C39" s="21" t="s">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="D39" s="22">
-        <v>0.01284614588917259</v>
+        <v>0.01843272641142624</v>
       </c>
     </row>
     <row r="40" spans="2:4">
       <c r="B40" s="20" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="C40" s="21" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="D40" s="22">
-        <v>0.0117492930757647</v>
+        <v>0.01118936779563407</v>
       </c>
     </row>
     <row r="41" spans="2:4">
       <c r="B41" s="20" t="s">
-        <v>202</v>
+        <v>193</v>
       </c>
       <c r="C41" s="21" t="s">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="D41" s="22">
-        <v>0.01034099356882087</v>
+        <v>0.0105736211291552</v>
       </c>
     </row>
     <row r="42" spans="2:4">
       <c r="B42" s="20" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="C42" s="21" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="D42" s="22">
-        <v>0.004495143173599308</v>
+        <v>0.009638106294655354</v>
       </c>
     </row>
     <row r="43" spans="2:4">
       <c r="B43" s="20" t="s">
-        <v>206</v>
+        <v>197</v>
       </c>
       <c r="C43" s="21" t="s">
-        <v>207</v>
+        <v>198</v>
       </c>
       <c r="D43" s="22">
-        <v>0.00276364734864643</v>
+        <v>0.003688594450444196</v>
       </c>
     </row>
     <row r="44" spans="2:4">
       <c r="B44" s="20" t="s">
-        <v>208</v>
+        <v>199</v>
       </c>
       <c r="C44" s="21" t="s">
-        <v>209</v>
+        <v>200</v>
       </c>
       <c r="D44" s="22">
-        <v>0.001539802502740401</v>
+        <v>0.001235830490370676</v>
       </c>
     </row>
     <row r="45" spans="2:4">
       <c r="B45" s="20" t="s">
-        <v>210</v>
+        <v>201</v>
       </c>
       <c r="C45" s="21" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="D45" s="22">
-        <v>0.0002051449930316286</v>
+        <v>0.000494344004491345</v>
       </c>
     </row>
     <row r="46" spans="2:4">
       <c r="B46" s="20" t="s">
-        <v>212</v>
+        <v>203</v>
       </c>
       <c r="C46" s="20" t="s">
-        <v>213</v>
+        <v>204</v>
       </c>
       <c r="D46" s="20" t="s">
-        <v>214</v>
+        <v>205</v>
       </c>
     </row>
   </sheetData>
@@ -3002,331 +2981,331 @@
     <row r="9" spans="1:22">
       <c r="A9" s="1"/>
       <c r="B9" s="9" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="C9" s="9" t="s">
-        <v>215</v>
+        <v>206</v>
       </c>
       <c r="D9" s="10">
-        <v>0.2075560647000804</v>
+        <v>0.1078759627361878</v>
       </c>
       <c r="E9" s="11" t="s">
-        <v>195</v>
+        <v>175</v>
       </c>
       <c r="F9" s="11" t="s">
-        <v>65</v>
+        <v>211</v>
       </c>
       <c r="G9" s="12">
-        <v>0.2460251057973028</v>
+        <v>0.4303602066704606</v>
       </c>
       <c r="H9" s="13" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="I9" s="13" t="s">
-        <v>224</v>
+        <v>216</v>
       </c>
       <c r="J9" s="14">
-        <v>0.3859309109702276</v>
+        <v>0.1149191591689172</v>
       </c>
       <c r="K9" s="15" t="s">
-        <v>189</v>
+        <v>177</v>
       </c>
       <c r="L9" s="15" t="s">
-        <v>229</v>
+        <v>221</v>
       </c>
       <c r="M9" s="16">
-        <v>0.09166075273117763</v>
+        <v>0.1187826580353412</v>
       </c>
       <c r="N9" s="17" t="s">
-        <v>189</v>
+        <v>173</v>
       </c>
       <c r="O9" s="17" t="s">
-        <v>234</v>
+        <v>226</v>
       </c>
       <c r="P9" s="18">
-        <v>0.1732478713132614</v>
+        <v>0.140019262215154</v>
       </c>
       <c r="Q9" s="15" t="s">
-        <v>193</v>
+        <v>173</v>
       </c>
       <c r="R9" s="15" t="s">
-        <v>239</v>
+        <v>231</v>
       </c>
       <c r="S9" s="16">
-        <v>0.1945885891687299</v>
+        <v>0.1731061363856942</v>
       </c>
       <c r="T9" s="17" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="U9" s="17" t="s">
-        <v>244</v>
+        <v>236</v>
       </c>
       <c r="V9" s="18">
-        <v>0.1942268759146094</v>
+        <v>0.09426478295197555</v>
       </c>
     </row>
     <row r="10" spans="1:22">
       <c r="A10" s="1"/>
       <c r="B10" s="9" t="s">
-        <v>187</v>
+        <v>177</v>
       </c>
       <c r="C10" s="9" t="s">
-        <v>216</v>
+        <v>207</v>
       </c>
       <c r="D10" s="10">
-        <v>0.09171203089780812</v>
+        <v>0.09148762431215397</v>
       </c>
       <c r="E10" s="11" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="F10" s="11" t="s">
-        <v>220</v>
+        <v>212</v>
       </c>
       <c r="G10" s="12">
-        <v>0.2006419448814319</v>
+        <v>0.0402552889310041</v>
       </c>
       <c r="H10" s="13" t="s">
-        <v>191</v>
+        <v>177</v>
       </c>
       <c r="I10" s="13" t="s">
-        <v>225</v>
+        <v>217</v>
       </c>
       <c r="J10" s="14">
-        <v>0.03424630283127828</v>
+        <v>0.08782422788634327</v>
       </c>
       <c r="K10" s="15" t="s">
-        <v>187</v>
+        <v>175</v>
       </c>
       <c r="L10" s="15" t="s">
-        <v>230</v>
+        <v>222</v>
       </c>
       <c r="M10" s="16">
-        <v>0.06694739211039991</v>
+        <v>0.111794642079307</v>
       </c>
       <c r="N10" s="17" t="s">
-        <v>187</v>
+        <v>175</v>
       </c>
       <c r="O10" s="17" t="s">
-        <v>235</v>
+        <v>227</v>
       </c>
       <c r="P10" s="18">
-        <v>0.09861110292469942</v>
+        <v>0.1023528907088976</v>
       </c>
       <c r="Q10" s="15" t="s">
-        <v>191</v>
+        <v>175</v>
       </c>
       <c r="R10" s="15" t="s">
-        <v>240</v>
+        <v>232</v>
       </c>
       <c r="S10" s="16">
-        <v>0.09104791757351917</v>
+        <v>0.07682361015381813</v>
       </c>
       <c r="T10" s="17" t="s">
-        <v>189</v>
+        <v>177</v>
       </c>
       <c r="U10" s="17" t="s">
-        <v>245</v>
+        <v>237</v>
       </c>
       <c r="V10" s="18">
-        <v>0.1137972252162375</v>
+        <v>0.08702619822847389</v>
       </c>
     </row>
     <row r="11" spans="1:22">
       <c r="A11" s="1"/>
       <c r="B11" s="9" t="s">
-        <v>189</v>
+        <v>173</v>
       </c>
       <c r="C11" s="9" t="s">
-        <v>217</v>
+        <v>208</v>
       </c>
       <c r="D11" s="10">
-        <v>0.07895404549153831</v>
+        <v>0.08872610436903326</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="F11" s="11" t="s">
-        <v>221</v>
+        <v>213</v>
       </c>
       <c r="G11" s="12">
-        <v>0.0528727646397812</v>
+        <v>0.03488223756809346</v>
       </c>
       <c r="H11" s="13" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="I11" s="13" t="s">
-        <v>226</v>
+        <v>218</v>
       </c>
       <c r="J11" s="14">
-        <v>0.01356586863534882</v>
+        <v>0.07196861975134038</v>
       </c>
       <c r="K11" s="15" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="L11" s="15" t="s">
-        <v>231</v>
+        <v>223</v>
       </c>
       <c r="M11" s="16">
-        <v>0.04656530819364679</v>
+        <v>0.09998771719301314</v>
       </c>
       <c r="N11" s="17" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="O11" s="17" t="s">
-        <v>236</v>
+        <v>228</v>
       </c>
       <c r="P11" s="18">
-        <v>0.0807473435844044</v>
+        <v>0.07945175091733891</v>
       </c>
       <c r="Q11" s="15" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="R11" s="15" t="s">
-        <v>241</v>
+        <v>233</v>
       </c>
       <c r="S11" s="16">
-        <v>0.0893039346133076</v>
+        <v>0.06310696496030381</v>
       </c>
       <c r="T11" s="17" t="s">
-        <v>183</v>
+        <v>173</v>
       </c>
       <c r="U11" s="17" t="s">
-        <v>246</v>
+        <v>238</v>
       </c>
       <c r="V11" s="18">
-        <v>0.01402445692311881</v>
+        <v>0.07900268773744588</v>
       </c>
     </row>
     <row r="12" spans="1:22">
       <c r="A12" s="1"/>
       <c r="B12" s="9" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="C12" s="9" t="s">
-        <v>218</v>
+        <v>209</v>
       </c>
       <c r="D12" s="10">
-        <v>0.02854000222162063</v>
+        <v>0.05076065826545611</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="F12" s="11" t="s">
-        <v>222</v>
+        <v>214</v>
       </c>
       <c r="G12" s="12">
-        <v>0.04506040827462476</v>
+        <v>0.02203495859950489</v>
       </c>
       <c r="H12" s="13" t="s">
-        <v>189</v>
+        <v>175</v>
       </c>
       <c r="I12" s="13" t="s">
-        <v>227</v>
+        <v>219</v>
       </c>
       <c r="J12" s="14">
-        <v>0.01309101672022986</v>
+        <v>0.05696357216295458</v>
       </c>
       <c r="K12" s="15" t="s">
-        <v>185</v>
+        <v>179</v>
       </c>
       <c r="L12" s="15" t="s">
-        <v>232</v>
+        <v>224</v>
       </c>
       <c r="M12" s="16">
-        <v>0.02721517727817786</v>
+        <v>0.06542440889865578</v>
       </c>
       <c r="N12" s="17" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="O12" s="17" t="s">
-        <v>237</v>
+        <v>229</v>
       </c>
       <c r="P12" s="18">
-        <v>0.07653236194591739</v>
+        <v>0.07557393571212855</v>
       </c>
       <c r="Q12" s="15" t="s">
-        <v>189</v>
+        <v>179</v>
       </c>
       <c r="R12" s="15" t="s">
-        <v>242</v>
+        <v>234</v>
       </c>
       <c r="S12" s="16">
-        <v>0.07530966713960631</v>
+        <v>0.05277135417370071</v>
       </c>
       <c r="T12" s="17" t="s">
-        <v>193</v>
+        <v>181</v>
       </c>
       <c r="U12" s="17" t="s">
-        <v>247</v>
+        <v>239</v>
       </c>
       <c r="V12" s="18">
-        <v>0.009986250674895314</v>
+        <v>0.06479201395403551</v>
       </c>
     </row>
     <row r="13" spans="1:22">
       <c r="A13" s="1"/>
       <c r="B13" s="9" t="s">
-        <v>193</v>
+        <v>181</v>
       </c>
       <c r="C13" s="9" t="s">
-        <v>219</v>
+        <v>210</v>
       </c>
       <c r="D13" s="10">
-        <v>0.01580448878487762</v>
+        <v>0.04925279944137553</v>
       </c>
       <c r="E13" s="11" t="s">
         <v>189</v>
       </c>
       <c r="F13" s="11" t="s">
-        <v>223</v>
+        <v>215</v>
       </c>
       <c r="G13" s="12">
-        <v>0.01209052269453475</v>
+        <v>0.01182599617871117</v>
       </c>
       <c r="H13" s="13" t="s">
         <v>187</v>
       </c>
       <c r="I13" s="13" t="s">
-        <v>228</v>
+        <v>220</v>
       </c>
       <c r="J13" s="14">
-        <v>0.01171397569552684</v>
+        <v>0.03408469709137366</v>
       </c>
       <c r="K13" s="15" t="s">
-        <v>193</v>
+        <v>181</v>
       </c>
       <c r="L13" s="15" t="s">
-        <v>233</v>
+        <v>225</v>
       </c>
       <c r="M13" s="16">
-        <v>0.01530242178794911</v>
+        <v>0.03514634407712686</v>
       </c>
       <c r="N13" s="17" t="s">
-        <v>191</v>
+        <v>181</v>
       </c>
       <c r="O13" s="17" t="s">
-        <v>238</v>
+        <v>230</v>
       </c>
       <c r="P13" s="18">
-        <v>0.02216423636807795</v>
+        <v>0.02818770230577704</v>
       </c>
       <c r="Q13" s="15" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="R13" s="15" t="s">
-        <v>243</v>
+        <v>235</v>
       </c>
       <c r="S13" s="16">
-        <v>0.02561916490966504</v>
+        <v>0.01097326982854985</v>
       </c>
       <c r="T13" s="17" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="U13" s="17" t="s">
-        <v>248</v>
+        <v>240</v>
       </c>
       <c r="V13" s="18">
-        <v>0.009643012943887055</v>
+        <v>0.02755924204979118</v>
       </c>
     </row>
     <row r="15" spans="1:22">
@@ -3337,7 +3316,7 @@
         <v>51</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D15" s="2" t="s">
         <v>53</v>
@@ -3346,7 +3325,7 @@
         <v>51</v>
       </c>
       <c r="F15" s="3" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="G15" s="3" t="s">
         <v>53</v>
@@ -3355,7 +3334,7 @@
         <v>51</v>
       </c>
       <c r="I15" s="4" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="J15" s="4" t="s">
         <v>53</v>
@@ -3364,7 +3343,7 @@
         <v>51</v>
       </c>
       <c r="L15" s="5" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="M15" s="5" t="s">
         <v>53</v>
@@ -3373,7 +3352,7 @@
         <v>51</v>
       </c>
       <c r="O15" s="6" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="P15" s="6" t="s">
         <v>53</v>
@@ -3382,7 +3361,7 @@
         <v>51</v>
       </c>
       <c r="R15" s="5" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="S15" s="5" t="s">
         <v>53</v>
@@ -3391,7 +3370,7 @@
         <v>51</v>
       </c>
       <c r="U15" s="6" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="V15" s="6" t="s">
         <v>53</v>
@@ -3400,331 +3379,331 @@
     <row r="16" spans="1:22">
       <c r="A16" s="1"/>
       <c r="B16" s="9" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="C16" s="9" t="s">
-        <v>249</v>
+        <v>241</v>
       </c>
       <c r="D16" s="10">
-        <v>0.2434545474255527</v>
+        <v>0.1556891937995099</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>195</v>
+        <v>175</v>
       </c>
       <c r="F16" s="11" t="s">
-        <v>127</v>
+        <v>246</v>
       </c>
       <c r="G16" s="12">
-        <v>0.2457599595633385</v>
+        <v>0.2511127586479147</v>
       </c>
       <c r="H16" s="13" t="s">
-        <v>183</v>
+        <v>175</v>
       </c>
       <c r="I16" s="13" t="s">
-        <v>258</v>
+        <v>251</v>
       </c>
       <c r="J16" s="14">
-        <v>0.4463006752324882</v>
+        <v>0.1540114057724394</v>
       </c>
       <c r="K16" s="15" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="L16" s="15" t="s">
-        <v>263</v>
+        <v>256</v>
       </c>
       <c r="M16" s="16">
-        <v>0.2134225769173123</v>
+        <v>0.121711487893027</v>
       </c>
       <c r="N16" s="17" t="s">
-        <v>185</v>
+        <v>175</v>
       </c>
       <c r="O16" s="17" t="s">
-        <v>268</v>
+        <v>261</v>
       </c>
       <c r="P16" s="18">
-        <v>0.2150422279977653</v>
+        <v>0.1458133739278843</v>
       </c>
       <c r="Q16" s="15" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="R16" s="15" t="s">
-        <v>273</v>
+        <v>266</v>
       </c>
       <c r="S16" s="16">
-        <v>0.1086819358802689</v>
+        <v>0.1944011896391575</v>
       </c>
       <c r="T16" s="17" t="s">
-        <v>187</v>
+        <v>173</v>
       </c>
       <c r="U16" s="17" t="s">
-        <v>278</v>
+        <v>271</v>
       </c>
       <c r="V16" s="18">
-        <v>0.4783883339453829</v>
+        <v>0.2371547466032021</v>
       </c>
     </row>
     <row r="17" spans="1:22">
       <c r="A17" s="1"/>
       <c r="B17" s="9" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="C17" s="9" t="s">
-        <v>250</v>
+        <v>242</v>
       </c>
       <c r="D17" s="10">
-        <v>0.08563205647192583</v>
+        <v>0.1271901076491316</v>
       </c>
       <c r="E17" s="11" t="s">
-        <v>189</v>
+        <v>173</v>
       </c>
       <c r="F17" s="11" t="s">
-        <v>254</v>
+        <v>247</v>
       </c>
       <c r="G17" s="12">
-        <v>0.09306247500126412</v>
+        <v>0.06176299256721179</v>
       </c>
       <c r="H17" s="13" t="s">
-        <v>185</v>
+        <v>173</v>
       </c>
       <c r="I17" s="13" t="s">
-        <v>259</v>
+        <v>252</v>
       </c>
       <c r="J17" s="14">
-        <v>0.02946246407663319</v>
+        <v>0.1454445944066547</v>
       </c>
       <c r="K17" s="15" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="L17" s="15" t="s">
-        <v>264</v>
+        <v>257</v>
       </c>
       <c r="M17" s="16">
-        <v>0.1947373219343786</v>
+        <v>0.1044165606764917</v>
       </c>
       <c r="N17" s="17" t="s">
-        <v>187</v>
+        <v>177</v>
       </c>
       <c r="O17" s="17" t="s">
-        <v>269</v>
+        <v>262</v>
       </c>
       <c r="P17" s="18">
-        <v>0.1140152677651115</v>
+        <v>0.1371226646535859</v>
       </c>
       <c r="Q17" s="15" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="R17" s="15" t="s">
-        <v>274</v>
+        <v>267</v>
       </c>
       <c r="S17" s="16">
-        <v>0.1075273951289696</v>
+        <v>0.09861761825961705</v>
       </c>
       <c r="T17" s="17" t="s">
-        <v>183</v>
+        <v>179</v>
       </c>
       <c r="U17" s="17" t="s">
-        <v>279</v>
+        <v>272</v>
       </c>
       <c r="V17" s="18">
-        <v>0.07842514301430584</v>
+        <v>0.1061732804694118</v>
       </c>
     </row>
     <row r="18" spans="1:22">
       <c r="A18" s="1"/>
       <c r="B18" s="9" t="s">
-        <v>189</v>
+        <v>173</v>
       </c>
       <c r="C18" s="9" t="s">
-        <v>251</v>
+        <v>243</v>
       </c>
       <c r="D18" s="10">
-        <v>0.07684458106253628</v>
+        <v>0.08037533901731232</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>185</v>
+        <v>177</v>
       </c>
       <c r="F18" s="11" t="s">
-        <v>255</v>
+        <v>248</v>
       </c>
       <c r="G18" s="12">
-        <v>0.04679180370093169</v>
+        <v>0.06010264822640844</v>
       </c>
       <c r="H18" s="13" t="s">
-        <v>187</v>
+        <v>177</v>
       </c>
       <c r="I18" s="13" t="s">
-        <v>260</v>
+        <v>253</v>
       </c>
       <c r="J18" s="14">
-        <v>0.02326952575119668</v>
+        <v>0.08450719552995475</v>
       </c>
       <c r="K18" s="15" t="s">
-        <v>189</v>
+        <v>175</v>
       </c>
       <c r="L18" s="15" t="s">
-        <v>265</v>
+        <v>258</v>
       </c>
       <c r="M18" s="16">
-        <v>0.1453390497684176</v>
+        <v>0.09182706605456967</v>
       </c>
       <c r="N18" s="17" t="s">
-        <v>189</v>
+        <v>173</v>
       </c>
       <c r="O18" s="17" t="s">
-        <v>270</v>
+        <v>263</v>
       </c>
       <c r="P18" s="18">
-        <v>0.07877942251654882</v>
+        <v>0.07366623043759304</v>
       </c>
       <c r="Q18" s="15" t="s">
-        <v>187</v>
+        <v>175</v>
       </c>
       <c r="R18" s="15" t="s">
-        <v>275</v>
+        <v>268</v>
       </c>
       <c r="S18" s="16">
-        <v>0.1075239951803005</v>
+        <v>0.0835899893647629</v>
       </c>
       <c r="T18" s="17" t="s">
-        <v>191</v>
+        <v>175</v>
       </c>
       <c r="U18" s="17" t="s">
-        <v>280</v>
+        <v>273</v>
       </c>
       <c r="V18" s="18">
-        <v>0.04266977930848994</v>
+        <v>0.09789286629020931</v>
       </c>
     </row>
     <row r="19" spans="1:22">
       <c r="A19" s="1"/>
       <c r="B19" s="9" t="s">
-        <v>191</v>
+        <v>187</v>
       </c>
       <c r="C19" s="9" t="s">
-        <v>252</v>
+        <v>244</v>
       </c>
       <c r="D19" s="10">
-        <v>0.05591591882864991</v>
+        <v>0.0628817167376218</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>187</v>
+        <v>179</v>
       </c>
       <c r="F19" s="11" t="s">
-        <v>256</v>
+        <v>249</v>
       </c>
       <c r="G19" s="12">
-        <v>0.02036083894543216</v>
+        <v>0.02777111377426799</v>
       </c>
       <c r="H19" s="13" t="s">
-        <v>189</v>
+        <v>179</v>
       </c>
       <c r="I19" s="13" t="s">
-        <v>261</v>
+        <v>254</v>
       </c>
       <c r="J19" s="14">
-        <v>0.01977677849222016</v>
+        <v>0.07545187004928836</v>
       </c>
       <c r="K19" s="15" t="s">
-        <v>191</v>
+        <v>179</v>
       </c>
       <c r="L19" s="15" t="s">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="M19" s="16">
-        <v>0.1401031262079092</v>
+        <v>0.0667333251315437</v>
       </c>
       <c r="N19" s="17" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="O19" s="17" t="s">
-        <v>271</v>
+        <v>264</v>
       </c>
       <c r="P19" s="18">
-        <v>0.06925193790540922</v>
+        <v>0.05277158879208513</v>
       </c>
       <c r="Q19" s="15" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="R19" s="15" t="s">
-        <v>276</v>
+        <v>269</v>
       </c>
       <c r="S19" s="16">
-        <v>0.07705072181048592</v>
+        <v>0.06534834624601248</v>
       </c>
       <c r="T19" s="17" t="s">
-        <v>189</v>
+        <v>177</v>
       </c>
       <c r="U19" s="17" t="s">
-        <v>281</v>
+        <v>274</v>
       </c>
       <c r="V19" s="18">
-        <v>0.02657228506174307</v>
+        <v>0.05478549973144996</v>
       </c>
     </row>
     <row r="20" spans="1:22">
       <c r="A20" s="1"/>
       <c r="B20" s="9" t="s">
-        <v>196</v>
+        <v>175</v>
       </c>
       <c r="C20" s="9" t="s">
-        <v>253</v>
+        <v>245</v>
       </c>
       <c r="D20" s="10">
-        <v>0.04297201417924287</v>
+        <v>0.04164077365100163</v>
       </c>
       <c r="E20" s="11" t="s">
         <v>183</v>
       </c>
       <c r="F20" s="11" t="s">
-        <v>257</v>
+        <v>250</v>
       </c>
       <c r="G20" s="12">
-        <v>0.008866942301626577</v>
+        <v>0.009232768270893612</v>
       </c>
       <c r="H20" s="13" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="I20" s="13" t="s">
-        <v>262</v>
+        <v>255</v>
       </c>
       <c r="J20" s="14">
-        <v>0.002996624199799406</v>
+        <v>0.02373951959013216</v>
       </c>
       <c r="K20" s="15" t="s">
-        <v>187</v>
+        <v>183</v>
       </c>
       <c r="L20" s="15" t="s">
-        <v>267</v>
+        <v>260</v>
       </c>
       <c r="M20" s="16">
-        <v>0.01479412413790095</v>
+        <v>0.03761321862849522</v>
       </c>
       <c r="N20" s="17" t="s">
-        <v>193</v>
+        <v>179</v>
       </c>
       <c r="O20" s="17" t="s">
-        <v>272</v>
+        <v>265</v>
       </c>
       <c r="P20" s="18">
-        <v>0.02133657444414968</v>
+        <v>0.04776481666535457</v>
       </c>
       <c r="Q20" s="15" t="s">
-        <v>189</v>
+        <v>179</v>
       </c>
       <c r="R20" s="15" t="s">
-        <v>277</v>
+        <v>270</v>
       </c>
       <c r="S20" s="16">
-        <v>0.03773008260275115</v>
+        <v>0.05827575791788995</v>
       </c>
       <c r="T20" s="17" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="U20" s="17" t="s">
-        <v>282</v>
+        <v>275</v>
       </c>
       <c r="V20" s="18">
-        <v>0.01205437671967047</v>
+        <v>0.03257907710059121</v>
       </c>
     </row>
   </sheetData>
